--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Creating Airflow Workflow/airflow_workflow_creation_questions.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Creating Airflow Workflow/airflow_workflow_creation_questions.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airflow Workflow Creation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>Explanation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -454,15 +454,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Import DAG module</t>
+          <t>Import DAG and operators from airflow.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Import DAG and operators from airflow.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -477,15 +476,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PythonOperator</t>
+          <t>PythonOperator executes Python callables.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PythonOperator executes Python callables.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -500,15 +498,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>&gt;&gt;</t>
+          <t>The bitshift operator defines task order.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The bitshift operator defines task order.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -523,15 +520,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A &gt;&gt; B</t>
+          <t>This creates a dependency where A runs before B.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>This creates a dependency where A runs before B.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -546,15 +542,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Execute bash commands</t>
+          <t>BashOperator runs bash commands or scripts.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BashOperator runs bash commands or scripts.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -569,15 +564,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Identify task</t>
+          <t>Each task must have a unique task_id within the DAG.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Each task must have a unique task_id within the DAG.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -599,12 +593,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>XComs allow tasks to exchange messages.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>XComs allow tasks to exchange messages.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -619,15 +613,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cross-communication</t>
+          <t>XCom stands for cross-communication between tasks.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>XCom stands for cross-communication between tasks.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -642,15 +635,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>xcom_push</t>
+          <t>xcom_push sends data to the XCom backend.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>xcom_push sends data to the XCom backend.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -665,15 +657,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>xcom_pull</t>
+          <t>xcom_pull retrieves data from the XCom backend.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>xcom_pull retrieves data from the XCom backend.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -688,15 +679,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48KB</t>
+          <t>The default limit is 48KB for performance reasons.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The default limit is 48KB for performance reasons.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -711,15 +701,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FileSensor</t>
+          <t>FileSensor checks for file existence.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FileSensor checks for file existence.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -734,15 +723,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Waiter</t>
+          <t>Sensors wait for a condition to be true.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sensors wait for a condition to be true.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -757,15 +745,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>retries parameter</t>
+          <t>Set retries in default_args or task level.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Set retries in default_args or task level.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -780,15 +767,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sequential runs</t>
+          <t>It prevents parallel execution of the same task.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>It prevents parallel execution of the same task.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -803,15 +789,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dependency chain</t>
+          <t>It ensures previous DAG run tasks complete.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>It ensures previous DAG run tasks complete.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -826,15 +811,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>@task</t>
+          <t>@task decorator simplifies Python function tasks.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>@task decorator simplifies Python function tasks.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -849,15 +833,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Simplified DAG definition</t>
+          <t>Taskflow API reduces boilerplate code.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Taskflow API reduces boilerplate code.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -879,12 +862,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Queued tasks indicate no workers are available.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Queued tasks indicate no workers are available.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -899,15 +882,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Conditional branching</t>
+          <t>BranchPythonOperator chooses next task based on condition.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BranchPythonOperator chooses next task based on condition.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
